--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_371_R38.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_371_R38.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0728</v>
+        <v>5.8033</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8122</v>
+        <v>3.5763</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2606</v>
+        <v>2.227</v>
       </c>
       <c r="G2" t="n">
         <v>4.6285</v>
@@ -610,13 +610,13 @@
         <v>3.4793</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3747</v>
+        <v>0.1052</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5351</v>
+        <v>0.2992</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1603</v>
+        <v>-0.1939</v>
       </c>
       <c r="V2" t="n">
         <v>0.1418</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. EBOUA</t>
+          <t>B. ANGOLA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0921</v>
+        <v>2.9701</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6565</v>
+        <v>1.0104</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4356</v>
+        <v>1.9597</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.0385</v>
+        <v>0.8539</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8453000000000001</v>
+        <v>1.7106</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.8838</v>
+        <v>-0.8567</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5024</v>
+        <v>2.1019</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6469</v>
+        <v>2.3765</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.1445</v>
+        <v>-0.2746</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5409</v>
+        <v>-1.248</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8016</v>
+        <v>-0.6659</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.5821</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0876</v>
+        <v>0.232</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3917</v>
+        <v>-3.7112</v>
       </c>
       <c r="R3" t="n">
-        <v>3.4793</v>
+        <v>3.9432</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9013</v>
+        <v>-0.402</v>
       </c>
       <c r="T3" t="n">
-        <v>1.404</v>
+        <v>-0.7387</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4973</v>
+        <v>0.3367</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1418</v>
+        <v>2.2862</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1418</v>
+        <v>3.3584</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. ANGOLA</t>
+          <t>D. LIGHTY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6828</v>
+        <v>2.6265</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4206</v>
+        <v>-1.1096</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2622</v>
+        <v>3.7361</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8539</v>
+        <v>0.3885</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7106</v>
+        <v>1.1212</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8567</v>
+        <v>-0.7327</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1019</v>
+        <v>0.1244</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3765</v>
+        <v>0.8003</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2746</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.248</v>
+        <v>0.2641</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6659</v>
+        <v>0.3209</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5821</v>
+        <v>-0.0568</v>
       </c>
       <c r="P4" t="n">
-        <v>0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.7112</v>
+        <v>-1.3917</v>
       </c>
       <c r="R4" t="n">
-        <v>3.9432</v>
+        <v>3.2473</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6893</v>
+        <v>0.3824</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3285</v>
+        <v>0.1577</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6392</v>
+        <v>0.2247</v>
       </c>
       <c r="V4" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3.3584</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. LIGHTY</t>
+          <t>P. EBOUA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5599</v>
+        <v>1.7452</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8737</v>
+        <v>-0.2871</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4337</v>
+        <v>2.0323</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3885</v>
+        <v>-1.0385</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1212</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7327</v>
+        <v>-1.8838</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1244</v>
+        <v>0.5024</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8003</v>
+        <v>1.6469</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-1.1445</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2641</v>
+        <v>-1.5409</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3209</v>
+        <v>-0.8016</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0568</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R5" t="n">
-        <v>3.2473</v>
+        <v>3.4793</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3159</v>
+        <v>0.5544</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3936</v>
+        <v>0.4604</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.07770000000000001</v>
+        <v>0.094</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>B. MASSA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7423</v>
+        <v>-0.7254</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0411</v>
+        <v>1.0359</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7012</v>
+        <v>-1.7613</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1344</v>
+        <v>1.0172</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4946</v>
+        <v>1.0708</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6291</v>
+        <v>-0.0535</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7527</v>
+        <v>1.5965</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0336</v>
+        <v>1.5965</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7863</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6183</v>
+        <v>-0.5792</v>
       </c>
       <c r="N6" t="n">
-        <v>0.461</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1573</v>
+        <v>-0.0535</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4643</v>
+        <v>0.1672</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7117</v>
+        <v>0.063</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2473</v>
+        <v>0.1041</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. MASSA</t>
+          <t>Z. SELJAAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0121</v>
+        <v>-0.9288</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6820000000000001</v>
+        <v>-1.6153</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6941</v>
+        <v>0.6864</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0172</v>
+        <v>-1.6008</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0708</v>
+        <v>-0.1319</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0535</v>
+        <v>-1.4689</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5965</v>
+        <v>-1.1358</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5965</v>
+        <v>0.4369</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.5727</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5792</v>
+        <v>-0.4651</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.5688</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0535</v>
+        <v>0.1038</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1195</v>
+        <v>-0.8098</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2908</v>
+        <v>-0.4795</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1713</v>
+        <v>-0.3304</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.214</v>
+        <v>-0.1418</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7501</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Z. SELJAAS</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1812</v>
+        <v>-1.1133</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7332</v>
+        <v>-0.5129</v>
       </c>
       <c r="F8" t="n">
-        <v>0.552</v>
+        <v>-0.6004</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6008</v>
+        <v>-0.1344</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1319</v>
+        <v>0.4946</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4689</v>
+        <v>-0.6291</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1358</v>
+        <v>-0.7527</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4369</v>
+        <v>0.0336</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.5727</v>
+        <v>-0.7863</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4651</v>
+        <v>0.6183</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5688</v>
+        <v>0.461</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1038</v>
+        <v>0.1573</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0622</v>
+        <v>0.0934</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5975</v>
+        <v>0.2399</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4648</v>
+        <v>-0.1465</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="9">
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1226</v>
+        <v>-2.8867</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2255</v>
+        <v>-1.9896</v>
       </c>
       <c r="F9" t="n">
         <v>-0.8971</v>
@@ -1156,10 +1156,10 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.456</v>
+        <v>-0.2201</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7468</v>
+        <v>-0.5109</v>
       </c>
       <c r="U9" t="n">
         <v>0.2908</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5098</v>
+        <v>-3.3418</v>
       </c>
       <c r="E10" t="n">
         <v>-3.3176</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1923</v>
+        <v>-0.0242</v>
       </c>
       <c r="G10" t="n">
         <v>-2.4263</v>
@@ -1234,13 +1234,13 @@
         <v>2.3195</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8</v>
+        <v>-0.6319</v>
       </c>
       <c r="T10" t="n">
         <v>-0.0272</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7727000000000001</v>
+        <v>-0.6047</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2836</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9788</v>
+        <v>-4.3726</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8752</v>
+        <v>-3.4034</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1036</v>
+        <v>-0.9692</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1561</v>
@@ -1312,13 +1312,13 @@
         <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6808999999999999</v>
+        <v>-0.0747</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1415</v>
+        <v>0.3304</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5395</v>
+        <v>-0.405</v>
       </c>
       <c r="V11" t="n">
         <v>-1.214</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.2477</v>
+        <v>-7.1633</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.1333</v>
+        <v>-6.0153</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1144</v>
+        <v>-1.148</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4573</v>
@@ -1390,13 +1390,13 @@
         <v>0.232</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.329</v>
+        <v>-0.2447</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5975</v>
+        <v>-0.4795</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2684</v>
+        <v>0.2348</v>
       </c>
       <c r="V12" t="n">
         <v>-1.214</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.386900000000001</v>
+        <v>-7.386799999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.6283</v>
+        <v>-12.6282</v>
       </c>
       <c r="F13" t="n">
-        <v>5.2414</v>
+        <v>5.2413</v>
       </c>
       <c r="G13" t="n">
         <v>-4.9836</v>
@@ -1468,13 +1468,13 @@
         <v>19.7161</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0807</v>
+        <v>-1.0806</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6854000000000002</v>
+        <v>-0.6852</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3952999999999999</v>
+        <v>-0.3954000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-3.642</v>
@@ -1483,7 +1483,7 @@
         <v>4.7142</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.356200000000001</v>
+        <v>-8.356199999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2835</v>
+        <v>4.2144</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9629</v>
+        <v>2.0809</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3205</v>
+        <v>2.1336</v>
       </c>
       <c r="G14" t="n">
         <v>1.9713</v>
@@ -1546,13 +1546,13 @@
         <v>2.7834</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4566</v>
+        <v>1.3875</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5034</v>
+        <v>0.6214</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9531</v>
+        <v>0.7662</v>
       </c>
       <c r="V14" t="n">
         <v>-0.5361</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.834</v>
+        <v>2.8226</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7398</v>
+        <v>0.5039</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0942</v>
+        <v>2.3187</v>
       </c>
       <c r="G15" t="n">
         <v>1.7864</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.022</v>
+        <v>-0.0334</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3462</v>
+        <v>0.1103</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3681</v>
+        <v>-0.1436</v>
       </c>
       <c r="V15" t="n">
         <v>0.1418</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3259</v>
+        <v>2.7406</v>
       </c>
       <c r="E16" t="n">
-        <v>2.168</v>
+        <v>1.9321</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1579</v>
+        <v>0.8085</v>
       </c>
       <c r="G16" t="n">
         <v>0.5395</v>
@@ -1702,13 +1702,13 @@
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1415</v>
+        <v>0.2732</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4208</v>
+        <v>0.1849</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5623</v>
+        <v>0.0883</v>
       </c>
       <c r="V16" t="n">
         <v>0.5361</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6345</v>
+        <v>1.9199</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.9967</v>
+        <v>-1.171</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6312</v>
+        <v>3.0909</v>
       </c>
       <c r="G17" t="n">
         <v>2.7035</v>
@@ -1780,13 +1780,13 @@
         <v>2.0876</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1233</v>
+        <v>0.1621</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8136</v>
+        <v>0.0121</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3097</v>
+        <v>0.15</v>
       </c>
       <c r="V17" t="n">
         <v>0.6778999999999999</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5597</v>
+        <v>0.7448</v>
       </c>
       <c r="E18" t="n">
-        <v>0.799</v>
+        <v>0.9169</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2393</v>
+        <v>-0.1721</v>
       </c>
       <c r="G18" t="n">
         <v>1.5094</v>
@@ -1858,13 +1858,13 @@
         <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2539</v>
+        <v>-0.0688</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1415</v>
+        <v>-0.0235</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1125</v>
+        <v>-0.0452</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. BOSTON JR.</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1198</v>
+        <v>0.1281</v>
       </c>
       <c r="E19" t="n">
-        <v>0.446</v>
+        <v>-2.4906</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5658</v>
+        <v>2.6187</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.8861</v>
+        <v>1.6044</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8187</v>
+        <v>-0.2461</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0673</v>
+        <v>1.8504</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9372</v>
+        <v>1.1299</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5986</v>
+        <v>1.2169</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.5359</v>
+        <v>-0.0871</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9488</v>
+        <v>0.4745</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.4174</v>
+        <v>-1.463</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4685</v>
+        <v>1.9375</v>
       </c>
       <c r="P19" t="n">
-        <v>0.232</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.3917</v>
+        <v>-3.7112</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S19" t="n">
-        <v>1.6039</v>
+        <v>0.1474</v>
       </c>
       <c r="T19" t="n">
-        <v>1.7027</v>
+        <v>0.0907</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0988</v>
+        <v>0.0567</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9304</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6157</v>
+        <v>-0.0881</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3651</v>
+        <v>-1.1292</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7494</v>
+        <v>1.0411</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7828</v>
@@ -2014,13 +2014,13 @@
         <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.0707</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5895</v>
+        <v>-0.3536</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.2829</v>
       </c>
       <c r="V20" t="n">
         <v>0.1418</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>T. HORTON TUCKER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7749</v>
+        <v>-0.1085</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6086</v>
+        <v>-2.9035</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8337</v>
+        <v>2.795</v>
       </c>
       <c r="G21" t="n">
-        <v>1.6044</v>
+        <v>-0.6976</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2461</v>
+        <v>-1.7617</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8504</v>
+        <v>1.0641</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1299</v>
+        <v>-2.1696</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2169</v>
+        <v>-1.2962</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0871</v>
+        <v>-0.8734</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4745</v>
+        <v>1.472</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.463</v>
+        <v>-0.4655</v>
       </c>
       <c r="O21" t="n">
         <v>1.9375</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.6237</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q21" t="n">
         <v>-3.7112</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7556</v>
+        <v>-0.1456</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0272</v>
+        <v>-0.3811</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7284</v>
+        <v>0.2355</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2.8223</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.3584</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. HORTON TUCKER</t>
+          <t>B. BOSTON JR.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8555</v>
+        <v>-0.9068000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4933</v>
+        <v>-0.7336</v>
       </c>
       <c r="F22" t="n">
-        <v>2.6378</v>
+        <v>-0.1733</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6976</v>
+        <v>-2.8861</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7617</v>
+        <v>-1.8187</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0641</v>
+        <v>-1.0673</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.1696</v>
+        <v>-0.9372</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2962</v>
+        <v>0.5986</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.8734</v>
+        <v>-1.5359</v>
       </c>
       <c r="M22" t="n">
-        <v>1.472</v>
+        <v>-1.9488</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4655</v>
+        <v>-2.4174</v>
       </c>
       <c r="O22" t="n">
-        <v>1.9375</v>
+        <v>0.4685</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.0876</v>
+        <v>0.232</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.7112</v>
+        <v>-1.3917</v>
       </c>
       <c r="R22" t="n">
         <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8927</v>
+        <v>0.8169</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9709</v>
+        <v>0.5232</v>
       </c>
       <c r="U22" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.2937</v>
       </c>
       <c r="V22" t="n">
-        <v>2.8223</v>
+        <v>0.9304</v>
       </c>
       <c r="W22" t="n">
-        <v>3.3584</v>
+        <v>1.0722</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8619</v>
+        <v>-1.0971</v>
       </c>
       <c r="E23" t="n">
         <v>-0.5473</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3146</v>
+        <v>-0.5498</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9959</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.134</v>
+        <v>-0.1013</v>
       </c>
       <c r="T23" t="n">
         <v>-0.2987</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4327</v>
+        <v>0.1975</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.023</v>
+        <v>-1.4104</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.3462</v>
+        <v>-1.7001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3232</v>
+        <v>0.2896</v>
       </c>
       <c r="G24" t="n">
         <v>1.2314</v>
@@ -2326,13 +2326,13 @@
         <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6734</v>
+        <v>0.286</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2636</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4099</v>
+        <v>0.3763</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>7.386800000000001</v>
+        <v>8.959500000000002</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.241499999999999</v>
+        <v>-5.2415</v>
       </c>
       <c r="F25" t="n">
-        <v>12.6282</v>
+        <v>14.2009</v>
       </c>
       <c r="G25" t="n">
-        <v>4.983500000000001</v>
+        <v>4.9835</v>
       </c>
       <c r="H25" t="n">
         <v>-8.132899999999999</v>
@@ -2404,13 +2404,13 @@
         <v>17.3966</v>
       </c>
       <c r="S25" t="n">
-        <v>1.0806</v>
+        <v>2.6533</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3953</v>
+        <v>0.3953999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6852999999999998</v>
+        <v>2.2583</v>
       </c>
       <c r="V25" t="n">
         <v>3.642</v>
